--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medication.xlsx
@@ -304,7 +304,7 @@
     <t>リソースに対するURLとして使われるリソースの論理ID。この値は一度割り当てられたら変更されることはない。</t>
   </si>
   <si>
-    <t>ResourceにIDがない時期は、create操作のためにサーバにResourceが送信されている時期だけである。</t>
+    <t>ResourceにIDがない時期は、create操作のためにサーバーにResourceが送信されている時期だけである。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -507,8 +507,8 @@
 使用法について注記：日本ではHOTコードを利用することが推奨される。一般的な薬剤コードとしてRxNorm、SNOMD CT, IDMPなど標準的な医薬品コードを使うことができる。国や地域に特有のローカルコードも使うことができ、他のコードに変換することもできる。</t>
   </si>
   <si>
-    <t>使われるコンテキストによるが、ユーザ(処方や調剤などを行った人）によって実際にコードが選択されたのであれば、coding.userSelectedはtrueとすることとなる。Codingのデータ型で説明されているように、「ユーザインターフェース（たとえば、選択肢から特定の項目をユーザが選択するような形式）で特定のコードをユーザが選択したのであれば、"userSelected"に記録されてもよい」  
-ユーザが選択したコードがあれば、その選択がコード変換などで優先される。そのほかのコードは代替のコードシステムか低粒度のコード（たとえば、ベンダー固有の初期値のための一般的なコード）に文字列変換変換するしかない。</t>
+    <t>使われるコンテキストによるが、ユーザー(処方や調剤などを行った人）によって実際にコードが選択されたのであれば、coding.userSelectedはtrueとすることとなる。Codingのデータ型で説明されているように、「ユーザーインターフェース（たとえば、選択肢から特定の項目をユーザーが選択するような形式）で特定のコードをユーザーが選択したのであれば、"userSelected"に記録されてもよい」  
+ユーザーが選択したコードがあれば、その選択がコード変換などで優先される。そのほかのコードは代替のコードシステムか低粒度のコード（たとえば、ベンダー固有の初期値のための一般的なコード）に文字列変換変換するしかない。</t>
   </si>
   <si>
     <t>薬品の種類を規定するコード化された概念</t>
